--- a/jogos_2025-02-19.xlsx
+++ b/jogos_2025-02-19.xlsx
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,22 +1417,22 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>El Kanemi Warriors</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bendel Insurance</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1443,83 +1443,83 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['1']</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['53']</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45707.45833333334</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,22 +1546,22 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>El Kanemi Warriors</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Bendel Insurance</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1572,83 +1572,83 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>['1']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>['53']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45707.45833333334</v>
@@ -1933,16 +1933,16 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sunshine Stars</t>
+          <t>Niger Tornadoes</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kano Pillars</t>
+          <t>Heartland</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
         <v>1</v>
@@ -1951,7 +1951,7 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1962,40 +1962,40 @@
         <v>1.53</v>
       </c>
       <c r="M12" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N12" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="O12" t="n">
         <v>2.2</v>
       </c>
       <c r="P12" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="Q12" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="R12" t="n">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="S12" t="n">
-        <v>2.33</v>
+        <v>2.22</v>
       </c>
       <c r="T12" t="n">
-        <v>3.9</v>
+        <v>3.58</v>
       </c>
       <c r="U12" t="n">
         <v>1.22</v>
       </c>
       <c r="V12" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="W12" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="X12" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="Y12" t="n">
         <v>2.6</v>
@@ -2004,35 +2004,35 @@
         <v>1.48</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.1</v>
+        <v>4.46</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>['59']</t>
+          <t>['59', '88']</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>['76']</t>
+          <t>['7']</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AJ12" t="n">
         <v>4.75</v>
@@ -2062,25 +2062,25 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Niger Tornadoes</t>
+          <t>Bayelsa United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Heartland</t>
+          <t>Nasarawa United</t>
         </is>
       </c>
       <c r="G13" t="n">
         <v>2</v>
       </c>
       <c r="H13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I13" t="n">
         <v>1</v>
       </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -2088,43 +2088,43 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="M13" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="N13" t="n">
+        <v>6</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q13" t="n">
         <v>6.5</v>
       </c>
-      <c r="O13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>7.5</v>
-      </c>
       <c r="R13" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="S13" t="n">
-        <v>2.22</v>
+        <v>2.38</v>
       </c>
       <c r="T13" t="n">
         <v>3.58</v>
       </c>
       <c r="U13" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="V13" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="W13" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="X13" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="Y13" t="n">
         <v>2.6</v>
@@ -2133,38 +2133,38 @@
         <v>1.48</v>
       </c>
       <c r="AA13" t="n">
-        <v>4.46</v>
+        <v>4.4</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>['59', '88']</t>
+          <t>['38', '90']</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>['7']</t>
+          <t>['2', '45+3']</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.23</v>
+        <v>2.05</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AJ13" t="n">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45707.5</v>
@@ -2191,109 +2191,109 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bayelsa United</t>
+          <t>Akwa United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nasarawa United</t>
+          <t>Rivers United</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
         <v>1</v>
       </c>
-      <c r="J14" t="n">
-        <v>2</v>
-      </c>
       <c r="K14" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.62</v>
+        <v>1.76</v>
       </c>
       <c r="M14" t="n">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="N14" t="n">
-        <v>6</v>
+        <v>4.91</v>
       </c>
       <c r="O14" t="n">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="P14" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.5</v>
+        <v>5.25</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="S14" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="T14" t="n">
-        <v>3.58</v>
+        <v>4.33</v>
       </c>
       <c r="U14" t="n">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="V14" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="W14" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="X14" t="n">
-        <v>2.41</v>
+        <v>2.14</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.6</v>
+        <v>2.85</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="AA14" t="n">
-        <v>4.4</v>
+        <v>6.75</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.18</v>
+        <v>1.04</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>['38', '90']</t>
+          <t>['54']</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>['2', '45+3']</t>
+          <t>['8']</t>
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.05</v>
+        <v>1.81</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="AJ14" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45707.5</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Akwa United</t>
+          <t>Sunshine Stars</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rivers United</t>
+          <t>Kano Pillars</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2338,7 +2338,7 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -2346,83 +2346,83 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.76</v>
+        <v>1.53</v>
       </c>
       <c r="M15" t="n">
-        <v>2.98</v>
+        <v>3.2</v>
       </c>
       <c r="N15" t="n">
-        <v>4.91</v>
+        <v>7</v>
       </c>
       <c r="O15" t="n">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="P15" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.25</v>
+        <v>7</v>
       </c>
       <c r="R15" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="S15" t="n">
-        <v>2.1</v>
+        <v>2.33</v>
       </c>
       <c r="T15" t="n">
-        <v>4.33</v>
+        <v>3.9</v>
       </c>
       <c r="U15" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="V15" t="n">
         <v>1.07</v>
       </c>
       <c r="W15" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="X15" t="n">
-        <v>2.14</v>
+        <v>2.32</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.85</v>
+        <v>2.6</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="AA15" t="n">
-        <v>6.75</v>
+        <v>5.1</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>['54']</t>
+          <t>['59']</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>['8']</t>
+          <t>['76']</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.81</v>
+        <v>2.17</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.58</v>
+        <v>1.4</v>
       </c>
       <c r="AJ15" t="n">
-        <v>3.2</v>
+        <v>4.75</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45707.5</v>
@@ -2449,22 +2449,22 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>US Biskra</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.61</v>
+        <v>2.47</v>
       </c>
       <c r="M16" t="n">
-        <v>3.41</v>
+        <v>2.88</v>
       </c>
       <c r="N16" t="n">
-        <v>6.4</v>
+        <v>3.14</v>
       </c>
       <c r="O16" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>5</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S16" t="n">
         <v>2.2</v>
       </c>
-      <c r="P16" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>7</v>
-      </c>
-      <c r="R16" t="n">
+      <c r="T16" t="n">
+        <v>4</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AI16" t="n">
         <v>1.57</v>
       </c>
-      <c r="S16" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="X16" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>['26']</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AJ16" t="n">
-        <v>4.33</v>
+        <v>3.1</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45707.54166666666</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,19 +2578,19 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Arenteiro</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Barakaldo CF</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G17" t="n">
         <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
         <v>1</v>
@@ -2604,28 +2604,28 @@
         </is>
       </c>
       <c r="L17" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="N17" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>7</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S17" t="n">
         <v>2.25</v>
-      </c>
-      <c r="M17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N17" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="O17" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.38</v>
       </c>
       <c r="T17" t="n">
         <v>3.75</v>
@@ -2634,53 +2634,53 @@
         <v>1.25</v>
       </c>
       <c r="V17" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="X17" t="n">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.37</v>
+        <v>2.65</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="AA17" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.1</v>
+        <v>2.75</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>['24']</t>
+          <t>['26']</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>['53']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.95</v>
+        <v>1.4</v>
       </c>
       <c r="AJ17" t="n">
-        <v>2.25</v>
+        <v>4.33</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45707.54166666666</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,22 +2707,22 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>US Biskra</t>
+          <t>Arenteiro</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Barakaldo CF</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2733,83 +2733,83 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.47</v>
+        <v>2.25</v>
       </c>
       <c r="M18" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="N18" t="n">
-        <v>3.14</v>
+        <v>2.9</v>
       </c>
       <c r="O18" t="n">
-        <v>2.63</v>
+        <v>3.4</v>
       </c>
       <c r="P18" t="n">
         <v>1.91</v>
       </c>
       <c r="Q18" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="R18" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="S18" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="T18" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="U18" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="V18" t="n">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="W18" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="X18" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>['24']</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>['53']</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ18" t="n">
         <v>2.25</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>3.1</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45707.54166666666</v>
@@ -3094,25 +3094,25 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I21" t="n">
         <v>1</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -3120,83 +3120,83 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.15</v>
+        <v>8.77</v>
       </c>
       <c r="M21" t="n">
-        <v>2.8</v>
+        <v>3.99</v>
       </c>
       <c r="N21" t="n">
-        <v>3.3</v>
+        <v>1.38</v>
       </c>
       <c r="O21" t="n">
-        <v>3</v>
+        <v>7.5</v>
       </c>
       <c r="P21" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="Q21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R21" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="S21" t="n">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="T21" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="U21" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="V21" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="W21" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="X21" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD21" t="n">
         <v>1.5</v>
       </c>
-      <c r="X21" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>['24', '53', '81', '86']</t>
+          <t>['37']</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>['4', '78']</t>
+          <t>['51', '79', '81']</t>
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.27</v>
+        <v>2.67</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.6</v>
+        <v>1.04</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.8</v>
+        <v>4.5</v>
       </c>
       <c r="AJ21" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45707.60416666666</v>
@@ -3223,25 +3223,25 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I22" t="n">
         <v>1</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -3249,83 +3249,83 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>8.77</v>
+        <v>2.15</v>
       </c>
       <c r="M22" t="n">
-        <v>3.99</v>
+        <v>2.8</v>
       </c>
       <c r="N22" t="n">
-        <v>1.38</v>
+        <v>3.3</v>
       </c>
       <c r="O22" t="n">
-        <v>7.5</v>
+        <v>3</v>
       </c>
       <c r="P22" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="Q22" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R22" t="n">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="S22" t="n">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="T22" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="U22" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="V22" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="W22" t="n">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="X22" t="n">
-        <v>2.78</v>
+        <v>2.3</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.72</v>
+        <v>5.1</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>['37']</t>
+          <t>['24', '53', '81', '86']</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>['51', '79', '81']</t>
+          <t>['4', '78']</t>
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>2.67</v>
+        <v>1.27</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.04</v>
+        <v>1.6</v>
       </c>
       <c r="AI22" t="n">
-        <v>4.5</v>
+        <v>1.8</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45707.60416666666</v>
@@ -4384,16 +4384,16 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>UCV</t>
+          <t>CD El Nacional</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
         <v>1</v>
@@ -4402,7 +4402,7 @@
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -4410,83 +4410,83 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>9</v>
+        <v>2.6</v>
       </c>
       <c r="M31" t="n">
-        <v>4.2</v>
+        <v>3.01</v>
       </c>
       <c r="N31" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="O31" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R31" t="n">
         <v>1.38</v>
       </c>
-      <c r="O31" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="P31" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.36</v>
-      </c>
       <c r="S31" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X31" t="n">
         <v>3</v>
       </c>
-      <c r="T31" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U31" t="n">
+      <c r="Y31" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>['78']</t>
+        </is>
+      </c>
+      <c r="AG31" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AH31" t="n">
         <v>1.44</v>
       </c>
-      <c r="V31" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X31" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC31" t="n">
+      <c r="AI31" t="n">
         <v>2.1</v>
       </c>
-      <c r="AD31" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE31" t="inlineStr">
-        <is>
-          <t>['75']</t>
-        </is>
-      </c>
-      <c r="AF31" t="inlineStr">
-        <is>
-          <t>['36']</t>
-        </is>
-      </c>
-      <c r="AG31" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>4.33</v>
-      </c>
       <c r="AJ31" t="n">
-        <v>1.29</v>
+        <v>2</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45707.89583333334</v>
@@ -4513,16 +4513,16 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>CD El Nacional</t>
+          <t>UCV</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32" t="n">
         <v>1</v>
@@ -4531,7 +4531,7 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -4539,83 +4539,83 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.6</v>
+        <v>9</v>
       </c>
       <c r="M32" t="n">
-        <v>3.01</v>
+        <v>4.2</v>
       </c>
       <c r="N32" t="n">
-        <v>2.37</v>
+        <v>1.38</v>
       </c>
       <c r="O32" t="n">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="P32" t="n">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="Q32" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X32" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA32" t="n">
         <v>3.1</v>
       </c>
-      <c r="R32" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S32" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V32" t="n">
+      <c r="AB32" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>['75']</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>['36']</t>
+        </is>
+      </c>
+      <c r="AG32" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AH32" t="n">
         <v>1.07</v>
       </c>
-      <c r="W32" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X32" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AE32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF32" t="inlineStr">
-        <is>
-          <t>['78']</t>
-        </is>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AI32" t="n">
-        <v>2.1</v>
+        <v>4.33</v>
       </c>
       <c r="AJ32" t="n">
-        <v>2</v>
+        <v>1.29</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45707.89583333334</v>
